--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4236-557-CM25</t>
+          <t>2408-4305-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5772.96</v>
+        <v>10304</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2408-4305-CM25</t>
+          <t>4236-557-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10304</v>
+        <v>5772.96</v>
       </c>
     </row>
     <row r="28">
@@ -2161,7 +2161,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1426098-219-CM25</t>
+          <t>2416-240-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4637.85</v>
+        <v>676.8099999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2416-241-CM25</t>
+          <t>1426098-219-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2280.5</v>
+        <v>4637.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2416-240-CM25</t>
+          <t>2416-241-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>676.8099999999999</v>
+        <v>2280.5</v>
       </c>
     </row>
     <row r="33">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2408-4606-CM25</t>
+          <t>2408-4607-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12879.97</v>
+        <v>4708.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2408-4607-CM25</t>
+          <t>2408-4606-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4708.37</v>
+        <v>12879.97</v>
       </c>
     </row>
     <row r="39">
@@ -3137,7 +3137,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2771-734-CM25</t>
+          <t>2771-735-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3896.58</v>
+        <v>5551.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2771-735-CM25</t>
+          <t>2771-734-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5551.25</v>
+        <v>3896.58</v>
       </c>
     </row>
     <row r="47">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2416-16-CM26</t>
+          <t>2945-141-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>24678.29</v>
+        <v>9012.629999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2416-20-CM26</t>
+          <t>3567-100-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7593.81</v>
+        <v>15543.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3945-133-CM26</t>
+          <t>2416-16-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIAL MODO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.712.337-K</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>13002.34</v>
+        <v>24678.29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1063796-7-CM26</t>
+          <t>3567-117-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>15117.48</v>
+        <v>3686.84</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4351-175-CM26</t>
+          <t>2416-20-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>692.95</v>
+        <v>7593.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1426098-120-CM26</t>
+          <t>3945-133-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL MODO SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.712.337-K</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7198.49</v>
+        <v>13002.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1426098-121-CM26</t>
+          <t>1063796-7-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2685.24</v>
+        <v>15117.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1208129-263-CM26</t>
+          <t>4351-175-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>280.29</v>
+        <v>692.95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4494-311-CM26</t>
+          <t>1426098-120-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,27 +4245,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>11580.57</v>
+        <v>7198.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2759-348-CM26</t>
+          <t>1426098-121-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1603.26</v>
+        <v>2685.24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057419-260-CM26</t>
+          <t>1208129-263-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,27 +4367,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.304-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>708.67</v>
+        <v>280.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4494-423-CM26</t>
+          <t>3567-277-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5293.07</v>
+        <v>56572.41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2785-467-CM26</t>
+          <t>4494-311-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4397.31</v>
+        <v>11580.57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1161266-450-CM26</t>
+          <t>2759-348-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.141.800-6</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1137.01</v>
+        <v>1603.26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3355-254-CM26</t>
+          <t>1057419-260-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,27 +4611,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.607.304-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>7238.98</v>
+        <v>708.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2408-702-CM26</t>
+          <t>4494-423-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>10808.54</v>
+        <v>5293.07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2759-738-CM26</t>
+          <t>2785-467-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2467.41</v>
+        <v>4397.31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1208129-410-CM26</t>
+          <t>1161266-450-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.141.800-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>204</v>
+        <v>1137.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4020-665-CM26</t>
+          <t>3355-254-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1752.6</v>
+        <v>7238.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4429-353-CM26</t>
+          <t>1063796-30-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.264.400-k</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>780.64</v>
+        <v>9081.540000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4020-667-CM26</t>
+          <t>2408-702-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2461.7</v>
+        <v>10808.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2408-780-CM26</t>
+          <t>2759-738-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>41293.81</v>
+        <v>2467.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3355-310-CM26</t>
+          <t>1208129-410-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,7 +5144,495 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4020-665-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.160.500-0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANETE</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>1752.6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4429-353-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.264.400-k</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>780.64</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4020-667-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.160.500-0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANETE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>2461.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2408-780-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>41293.81</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3355-310-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.101.076-1</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>7291.09</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1161266-639-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.141.800-6</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>325.06</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1036-244-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>154.85</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2408-980-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>7212.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
@@ -623,7 +623,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +997,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1700,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1952,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2143,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2208,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2456,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2708,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2773,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2838,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2903,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3029,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3094,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3159,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3224,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3289,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3354,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3419,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3484,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3549,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3614,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3740,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3805,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3870,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4057,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4183,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4248,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4313,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4561,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4687,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4752,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4817,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4943,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5008,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5073,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5138,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5203,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5268,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5333,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5398,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5463,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5528,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5593,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5658,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5723,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5788,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5853,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2286,7 +2286,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2416-242-CM25</t>
+          <t>2416-241-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2326,28 +2326,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5283.49</v>
+        <v>2280.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1426098-219-CM25</t>
+          <t>2416-242-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2372,12 +2376,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2387,12 +2391,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2402,13 +2406,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4637.85</v>
+        <v>5283.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2416-241-CM25</t>
+          <t>1426098-219-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2433,12 +2437,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2448,26 +2452,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2280.5</v>
+        <v>4637.85</v>
       </c>
     </row>
     <row r="33">
@@ -4391,7 +4391,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1426098-120-CM26</t>
+          <t>1426098-121-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7198.49</v>
+        <v>2685.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1426098-121-CM26</t>
+          <t>1426098-120-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2685.24</v>
+        <v>7198.49</v>
       </c>
     </row>
     <row r="65">
@@ -4639,7 +4639,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4494-311-CM26</t>
+          <t>2759-348-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11580.57</v>
+        <v>1603.26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2759-348-CM26</t>
+          <t>4494-311-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1603.26</v>
+        <v>11580.57</v>
       </c>
     </row>
     <row r="69">
@@ -5285,7 +5285,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1208129-410-CM26</t>
+          <t>4020-665-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5305,17 +5305,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5344,13 +5344,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>204</v>
+        <v>1752.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4020-665-CM26</t>
+          <t>1208129-410-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1752.6</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4429-353-CM26</t>
+          <t>4020-667-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5435,17 +5435,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.264.400-k</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5474,13 +5474,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>780.64</v>
+        <v>2461.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4020-667-CM26</t>
+          <t>4429-353-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5500,17 +5500,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.264.400-k</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2461.7</v>
+        <v>780.64</v>
       </c>
     </row>
     <row r="81">
@@ -5740,7 +5740,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1036-244-CM26</t>
+          <t>1036-241-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5780,26 +5780,22 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>154.85</v>
+        <v>5615.13</v>
       </c>
     </row>
     <row r="85">
@@ -5865,6 +5861,396 @@
       </c>
       <c r="M85" s="2" t="n">
         <v>7212.27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1036-244-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>154.85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1063796-42-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.150.400-k</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>7389.36</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2416-272-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>7079.53</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2408-1069-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>10013.46</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4236-780-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>69.160.200-1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>8478.030000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1057404-1399-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.602.209-1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1238.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
@@ -4789,7 +4789,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -884,7 +884,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2785-57-CM25</t>
+          <t>2785-56-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KUB CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.820.166-6</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2062.12</v>
+        <v>6943.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2785-56-CM25</t>
+          <t>2785-57-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>KUB CHILE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.820.166-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6943.63</v>
+        <v>2062.12</v>
       </c>
     </row>
     <row r="10">
@@ -1274,7 +1274,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1426098-82-CM25</t>
+          <t>2408-3831-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1314,28 +1314,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3414.76</v>
+        <v>39018.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408-3831-CM25</t>
+          <t>1426098-82-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1360,12 +1364,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1375,26 +1379,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>39018.38</v>
+        <v>3414.76</v>
       </c>
     </row>
     <row r="16">
@@ -3371,7 +3371,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2785-4508-CM25</t>
+          <t>2785-4509-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4696.48</v>
+        <v>1688.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2785-4509-CM25</t>
+          <t>2785-4508-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1688.66</v>
+        <v>4696.48</v>
       </c>
     </row>
     <row r="49">
@@ -5415,7 +5415,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4020-667-CM26</t>
+          <t>4429-353-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.264.400-k</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5474,13 +5474,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2461.7</v>
+        <v>780.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4429-353-CM26</t>
+          <t>4020-667-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.264.400-k</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>780.64</v>
+        <v>2461.7</v>
       </c>
     </row>
     <row r="81">
@@ -6251,6 +6251,262 @@
       </c>
       <c r="M91" s="2" t="n">
         <v>1238.27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2415-267-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>6630.55</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1057404-1401-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.602.209-1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>1233.56</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4236-794-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.160.200-1</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>8966.43</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4351-488-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>69.170.700-8</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>853.11</v>
       </c>
     </row>
   </sheetData>
